--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T08:03:06+00:00</t>
+    <t>2026-07-13T08:07:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T08:07:14+00:00</t>
+    <t>2026-07-13T09:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:42:02+00:00</t>
+    <t>2026-07-13T09:54:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:54:52+00:00</t>
+    <t>2026-07-13T10:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T10:08:48+00:00</t>
+    <t>2026-07-13T11:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T11:40:01+00:00</t>
+    <t>2026-07-13T12:00:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T12:00:20+00:00</t>
+    <t>2026-07-13T12:22:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T12:22:37+00:00</t>
+    <t>2026-07-13T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T12:35:36+00:00</t>
+    <t>2026-07-15T07:17:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T07:17:36+00:00</t>
+    <t>2026-07-15T07:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T07:29:40+00:00</t>
+    <t>2026-07-15T07:41:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T07:41:29+00:00</t>
+    <t>2026-07-15T08:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
+++ b/feature/change-regulator-schema-to-mermaid/ig/StructureDefinition-sas-cpts-slot-aggregator.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T08:14:55+00:00</t>
+    <t>2026-07-15T08:26:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
